--- a/backend/samples/sample_invoice.xlsx
+++ b/backend/samples/sample_invoice.xlsx
@@ -7,7 +7,7 @@
     <workbookView visibility="visible" minimized="0" showHorizontalScroll="1" showVerticalScroll="1" showSheetTabs="1" tabRatio="600" firstSheet="0" activeTab="0" autoFilterDateGrouping="1"/>
   </bookViews>
   <sheets>
-    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Tax Invoice" sheetId="1" state="visible" r:id="rId1"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Bill" sheetId="1" state="visible" r:id="rId1"/>
   </sheets>
   <definedNames/>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
@@ -16,10 +16,8 @@
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
-  <numFmts count="1">
-    <numFmt numFmtId="164" formatCode="$#,##0.00"/>
-  </numFmts>
-  <fonts count="7">
+  <numFmts count="0"/>
+  <fonts count="4">
     <font>
       <name val="Calibri"/>
       <family val="2"/>
@@ -28,41 +26,21 @@
       <scheme val="minor"/>
     </font>
     <font>
-      <name val="Segoe UI"/>
+      <name val="Calibri"/>
       <b val="1"/>
-      <color rgb="001E3A8A"/>
-      <sz val="16"/>
+      <sz val="11"/>
     </font>
     <font>
-      <name val="Segoe UI"/>
-      <color rgb="004B5563"/>
+      <name val="Calibri"/>
       <sz val="10"/>
     </font>
     <font>
-      <name val="Segoe UI"/>
+      <name val="Calibri"/>
       <b val="1"/>
-      <color rgb="00111827"/>
-      <sz val="10"/>
-    </font>
-    <font>
-      <name val="Segoe UI"/>
-      <color rgb="001F2937"/>
-      <sz val="10"/>
-    </font>
-    <font>
-      <name val="Segoe UI"/>
-      <b val="1"/>
-      <color rgb="00FFFFFF"/>
-      <sz val="10"/>
-    </font>
-    <font>
-      <name val="Segoe UI"/>
-      <b val="1"/>
-      <color rgb="001E3A8A"/>
-      <sz val="11"/>
+      <sz val="15"/>
     </font>
   </fonts>
-  <fills count="5">
+  <fills count="3">
     <fill>
       <patternFill/>
     </fill>
@@ -71,24 +49,12 @@
     </fill>
     <fill>
       <patternFill patternType="solid">
-        <fgColor rgb="001E3A8A"/>
-        <bgColor rgb="001E3A8A"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="00F9FAFB"/>
-        <bgColor rgb="00F9FAFB"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="00EFF6FF"/>
-        <bgColor rgb="00EFF6FF"/>
+        <fgColor rgb="00F1F5F9"/>
+        <bgColor rgb="00F1F5F9"/>
       </patternFill>
     </fill>
   </fills>
-  <borders count="3">
+  <borders count="2">
     <border>
       <left/>
       <right/>
@@ -98,81 +64,51 @@
     </border>
     <border>
       <left style="thin">
-        <color rgb="00D1D5DB"/>
+        <color rgb="00CBD5E1"/>
       </left>
       <right style="thin">
-        <color rgb="00D1D5DB"/>
+        <color rgb="00CBD5E1"/>
       </right>
       <top style="thin">
-        <color rgb="00D1D5DB"/>
+        <color rgb="00CBD5E1"/>
       </top>
       <bottom style="thin">
-        <color rgb="00D1D5DB"/>
-      </bottom>
-    </border>
-    <border>
-      <top style="thin">
-        <color rgb="00D1D5DB"/>
-      </top>
-      <bottom style="double">
-        <color rgb="001E3A8A"/>
+        <color rgb="00CBD5E1"/>
       </bottom>
     </border>
   </borders>
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="20">
+  <cellXfs count="14">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="0" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="3" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
-    <xf numFmtId="0" fontId="4" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
-    <xf numFmtId="0" fontId="4" fillId="0" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="right"/>
     </xf>
-    <xf numFmtId="0" fontId="5" fillId="2" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="5" fillId="2" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
-      <alignment horizontal="left" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="5" fillId="2" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
-      <alignment horizontal="right" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="4" fillId="0" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="0" fontId="3" fillId="0" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="center"/>
     </xf>
-    <xf numFmtId="0" fontId="4" fillId="0" borderId="1" pivotButton="0" quotePrefix="0" xfId="0"/>
-    <xf numFmtId="164" fontId="4" fillId="0" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+    <xf numFmtId="0" fontId="1" fillId="2" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="2" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="left"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="2" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="right"/>
     </xf>
-    <xf numFmtId="0" fontId="4" fillId="3" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="center"/>
     </xf>
-    <xf numFmtId="0" fontId="4" fillId="3" borderId="1" pivotButton="0" quotePrefix="0" xfId="0"/>
-    <xf numFmtId="164" fontId="4" fillId="3" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="1" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="4" fontId="2" fillId="0" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="right"/>
     </xf>
-    <xf numFmtId="0" fontId="3" fillId="0" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
-      <alignment horizontal="right"/>
-    </xf>
-    <xf numFmtId="164" fontId="3" fillId="0" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
-      <alignment horizontal="right"/>
-    </xf>
-    <xf numFmtId="164" fontId="4" fillId="0" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
-      <alignment horizontal="right"/>
-    </xf>
-    <xf numFmtId="0" fontId="6" fillId="4" borderId="2" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
-      <alignment horizontal="right" vertical="center"/>
-    </xf>
-    <xf numFmtId="164" fontId="6" fillId="4" borderId="2" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
-      <alignment horizontal="right" vertical="center"/>
-    </xf>
+    <xf numFmtId="0" fontId="0" fillId="2" borderId="1" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="0" fontId="1" fillId="2" borderId="1" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="4" fontId="1" fillId="2" borderId="1" pivotButton="0" quotePrefix="0" xfId="0"/>
   </cellXfs>
   <cellStyles count="1">
     <cellStyle name="Normal" xfId="0" builtinId="0" hidden="0"/>
@@ -536,350 +472,461 @@
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <sheetPr>
     <outlinePr summaryBelow="1" summaryRight="1"/>
-    <pageSetUpPr fitToPage="1"/>
+    <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A2:E31"/>
+  <dimension ref="A4:F36"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="6" customWidth="1" min="1" max="1"/>
-    <col width="30" customWidth="1" min="2" max="2"/>
-    <col width="12" customWidth="1" min="3" max="3"/>
-    <col width="14" customWidth="1" min="4" max="4"/>
+    <col width="34" customWidth="1" min="2" max="2"/>
+    <col width="11" customWidth="1" min="3" max="3"/>
+    <col width="12" customWidth="1" min="4" max="4"/>
     <col width="16" customWidth="1" min="5" max="5"/>
+    <col width="18" customWidth="1" min="6" max="6"/>
   </cols>
   <sheetData>
-    <row r="2" ht="28" customHeight="1">
-      <c r="A2" s="1" t="inlineStr">
-        <is>
-          <t>COMMERCIAL INVOICE</t>
-        </is>
-      </c>
-    </row>
-    <row r="3">
-      <c r="A3" s="2" t="inlineStr">
-        <is>
-          <t>Original For Recipient | GST/VAT Compliant</t>
-        </is>
-      </c>
-    </row>
-    <row r="5">
-      <c r="A5" s="3" t="inlineStr">
-        <is>
-          <t>Invoice No:</t>
-        </is>
-      </c>
-      <c r="B5" s="4" t="inlineStr">
-        <is>
-          <t>INV-2026-0842</t>
-        </is>
-      </c>
-      <c r="D5" s="3" t="inlineStr">
-        <is>
-          <t>Invoice Date:</t>
-        </is>
-      </c>
-      <c r="E5" s="5" t="inlineStr">
-        <is>
-          <t>18-Oct-2026</t>
+    <row r="1" ht="20" customHeight="1"/>
+    <row r="2" ht="20" customHeight="1"/>
+    <row r="3" ht="15" customHeight="1"/>
+    <row r="4">
+      <c r="B4" s="1" t="inlineStr">
+        <is>
+          <t>Ref: W.B/Bill # 0072/26</t>
+        </is>
+      </c>
+      <c r="F4" s="2" t="inlineStr">
+        <is>
+          <t>Date: 14.06.2026</t>
         </is>
       </c>
     </row>
     <row r="6">
-      <c r="A6" s="3" t="inlineStr">
-        <is>
-          <t>Due Date:</t>
-        </is>
-      </c>
-      <c r="B6" s="4" t="inlineStr">
-        <is>
-          <t>02-Nov-2026</t>
-        </is>
-      </c>
-      <c r="D6" s="3" t="inlineStr">
-        <is>
-          <t>Payment Terms:</t>
-        </is>
-      </c>
-      <c r="E6" s="5" t="inlineStr">
-        <is>
-          <t>Net 15 Days</t>
+      <c r="B6" s="1" t="inlineStr">
+        <is>
+          <t>To</t>
+        </is>
+      </c>
+    </row>
+    <row r="7">
+      <c r="B7" s="1" t="inlineStr">
+        <is>
+          <t>The World Bank Office</t>
         </is>
       </c>
     </row>
     <row r="8">
-      <c r="A8" s="3" t="inlineStr">
-        <is>
-          <t>Billed To:</t>
-        </is>
-      </c>
       <c r="B8" s="3" t="inlineStr">
         <is>
-          <t>Horizon Global Enterprises Ltd.</t>
+          <t>Plot # E-32, Agargoan</t>
         </is>
       </c>
     </row>
     <row r="9">
-      <c r="B9" s="4" t="inlineStr">
-        <is>
-          <t>450 Innovation Parkway, Suite 800</t>
-        </is>
-      </c>
-    </row>
-    <row r="10">
-      <c r="B10" s="4" t="inlineStr">
-        <is>
-          <t>San Francisco, CA 94107</t>
-        </is>
-      </c>
-    </row>
-    <row r="11">
-      <c r="B11" s="4" t="inlineStr">
-        <is>
-          <t>Attn: Accounts Payable (finance@horizonglobal.com)</t>
-        </is>
-      </c>
-    </row>
-    <row r="13" ht="24" customHeight="1">
-      <c r="A13" s="6" t="inlineStr">
-        <is>
-          <t>#</t>
-        </is>
-      </c>
-      <c r="B13" s="7" t="inlineStr">
-        <is>
-          <t>Item Description</t>
-        </is>
-      </c>
-      <c r="C13" s="6" t="inlineStr">
-        <is>
-          <t>Qty</t>
-        </is>
-      </c>
-      <c r="D13" s="8" t="inlineStr">
-        <is>
-          <t>Unit Price</t>
-        </is>
-      </c>
-      <c r="E13" s="8" t="inlineStr">
-        <is>
-          <t>Total (USD)</t>
-        </is>
-      </c>
-    </row>
-    <row r="14" ht="20" customHeight="1">
-      <c r="A14" s="9" t="n">
+      <c r="B9" s="3" t="inlineStr">
+        <is>
+          <t>Sher-e-Bangla Nagar, Dhaka.</t>
+        </is>
+      </c>
+    </row>
+    <row r="12">
+      <c r="B12" s="4" t="inlineStr">
+        <is>
+          <t>Bill for Supply Items</t>
+        </is>
+      </c>
+    </row>
+    <row r="14">
+      <c r="A14" s="5" t="inlineStr">
+        <is>
+          <t>SI#</t>
+        </is>
+      </c>
+      <c r="B14" s="6" t="inlineStr">
+        <is>
+          <t>Item Name &amp; Description</t>
+        </is>
+      </c>
+      <c r="C14" s="5" t="inlineStr">
+        <is>
+          <t>Quantity</t>
+        </is>
+      </c>
+      <c r="D14" s="5" t="inlineStr">
+        <is>
+          <t>Pack Size</t>
+        </is>
+      </c>
+      <c r="E14" s="7" t="inlineStr">
+        <is>
+          <t>Unit Price (BDT)</t>
+        </is>
+      </c>
+      <c r="F14" s="7" t="inlineStr">
+        <is>
+          <t>Total Amount (BDT)</t>
+        </is>
+      </c>
+    </row>
+    <row r="15">
+      <c r="A15" s="8" t="n">
         <v>1</v>
       </c>
-      <c r="B14" s="10" t="inlineStr">
-        <is>
-          <t>Enterprise Cloud Architecture Consulting</t>
-        </is>
-      </c>
-      <c r="C14" s="9" t="n">
-        <v>40</v>
-      </c>
-      <c r="D14" s="11" t="n">
-        <v>150</v>
-      </c>
-      <c r="E14" s="11">
-        <f>C14*D14</f>
+      <c r="B15" s="9" t="inlineStr">
+        <is>
+          <t>Ispahani Tea Bags</t>
+        </is>
+      </c>
+      <c r="C15" s="8" t="n">
+        <v>127</v>
+      </c>
+      <c r="D15" s="8" t="inlineStr">
+        <is>
+          <t>50 Bags</t>
+        </is>
+      </c>
+      <c r="E15" s="10" t="n">
+        <v>94</v>
+      </c>
+      <c r="F15" s="10" t="n">
+        <v>11938</v>
+      </c>
+    </row>
+    <row r="16">
+      <c r="A16" s="8" t="n">
+        <v>2</v>
+      </c>
+      <c r="B16" s="9" t="inlineStr">
+        <is>
+          <t>Nescafe Classic Coffee</t>
+        </is>
+      </c>
+      <c r="C16" s="8" t="n">
+        <v>24</v>
+      </c>
+      <c r="D16" s="8" t="inlineStr">
+        <is>
+          <t>200 gm</t>
+        </is>
+      </c>
+      <c r="E16" s="10" t="n">
+        <v>950</v>
+      </c>
+      <c r="F16" s="10" t="n">
+        <v>22800</v>
+      </c>
+    </row>
+    <row r="17">
+      <c r="A17" s="8" t="n">
+        <v>3</v>
+      </c>
+      <c r="B17" s="9" t="inlineStr">
+        <is>
+          <t>Diploma Full Cream Powder Milk</t>
+        </is>
+      </c>
+      <c r="C17" s="8" t="n">
+        <v>24</v>
+      </c>
+      <c r="D17" s="8" t="inlineStr">
+        <is>
+          <t>1 kg</t>
+        </is>
+      </c>
+      <c r="E17" s="10" t="n">
+        <v>935</v>
+      </c>
+      <c r="F17" s="10" t="n">
+        <v>22440</v>
+      </c>
+    </row>
+    <row r="18">
+      <c r="A18" s="8" t="n">
+        <v>4</v>
+      </c>
+      <c r="B18" s="9" t="inlineStr">
+        <is>
+          <t>Fresh White Sugar</t>
+        </is>
+      </c>
+      <c r="C18" s="8" t="n">
+        <v>51</v>
+      </c>
+      <c r="D18" s="8" t="inlineStr">
+        <is>
+          <t>1 kg</t>
+        </is>
+      </c>
+      <c r="E18" s="10" t="n">
+        <v>104</v>
+      </c>
+      <c r="F18" s="10" t="n">
+        <v>5304</v>
+      </c>
+    </row>
+    <row r="19">
+      <c r="A19" s="8" t="n">
+        <v>5</v>
+      </c>
+      <c r="B19" s="9" t="inlineStr">
+        <is>
+          <t>Canderel Sweetener (Square)</t>
+        </is>
+      </c>
+      <c r="C19" s="8" t="n">
+        <v>8</v>
+      </c>
+      <c r="D19" s="8" t="inlineStr">
+        <is>
+          <t>100 Tab</t>
+        </is>
+      </c>
+      <c r="E19" s="10" t="n">
+        <v>115</v>
+      </c>
+      <c r="F19" s="10" t="n">
+        <v>920</v>
+      </c>
+    </row>
+    <row r="20">
+      <c r="A20" s="8" t="n">
+        <v>6</v>
+      </c>
+      <c r="B20" s="9" t="inlineStr">
+        <is>
+          <t>Liquid Vim Dishwashing</t>
+        </is>
+      </c>
+      <c r="C20" s="8" t="n">
+        <v>15</v>
+      </c>
+      <c r="D20" s="8" t="inlineStr">
+        <is>
+          <t>500 ml</t>
+        </is>
+      </c>
+      <c r="E20" s="10" t="n">
+        <v>125</v>
+      </c>
+      <c r="F20" s="10" t="n">
+        <v>1875</v>
+      </c>
+    </row>
+    <row r="21">
+      <c r="A21" s="8" t="n">
+        <v>7</v>
+      </c>
+      <c r="B21" s="9" t="inlineStr">
+        <is>
+          <t>Jet Washing Powder</t>
+        </is>
+      </c>
+      <c r="C21" s="8" t="n">
+        <v>3</v>
+      </c>
+      <c r="D21" s="8" t="inlineStr">
+        <is>
+          <t>1 kg</t>
+        </is>
+      </c>
+      <c r="E21" s="10" t="n">
+        <v>280</v>
+      </c>
+      <c r="F21" s="10" t="n">
+        <v>840</v>
+      </c>
+    </row>
+    <row r="22">
+      <c r="A22" s="8" t="n">
+        <v>8</v>
+      </c>
+      <c r="B22" s="9" t="inlineStr">
+        <is>
+          <t>Lux Beauty Soap</t>
+        </is>
+      </c>
+      <c r="C22" s="8" t="n">
+        <v>6</v>
+      </c>
+      <c r="D22" s="8" t="inlineStr">
+        <is>
+          <t>100 gm</t>
+        </is>
+      </c>
+      <c r="E22" s="10" t="n">
+        <v>55</v>
+      </c>
+      <c r="F22" s="10" t="n">
+        <v>330</v>
+      </c>
+    </row>
+    <row r="23">
+      <c r="A23" s="8" t="n">
+        <v>9</v>
+      </c>
+      <c r="B23" s="9" t="inlineStr">
+        <is>
+          <t>Air Freshener (Godrej)</t>
+        </is>
+      </c>
+      <c r="C23" s="8" t="n">
+        <v>7</v>
+      </c>
+      <c r="D23" s="8" t="inlineStr">
+        <is>
+          <t>300 ml</t>
+        </is>
+      </c>
+      <c r="E23" s="10" t="n">
+        <v>280</v>
+      </c>
+      <c r="F23" s="10" t="n">
+        <v>1960</v>
+      </c>
+    </row>
+    <row r="24">
+      <c r="A24" s="8" t="n">
+        <v>10</v>
+      </c>
+      <c r="B24" s="9" t="inlineStr">
+        <is>
+          <t>ACI Aerosol Spray</t>
+        </is>
+      </c>
+      <c r="C24" s="8" t="n">
+        <v>5</v>
+      </c>
+      <c r="D24" s="8" t="inlineStr">
+        <is>
+          <t>475 ml</t>
+        </is>
+      </c>
+      <c r="E24" s="10" t="n">
+        <v>400</v>
+      </c>
+      <c r="F24" s="10" t="n">
+        <v>2000</v>
+      </c>
+    </row>
+    <row r="25">
+      <c r="A25" s="8" t="n">
+        <v>11</v>
+      </c>
+      <c r="B25" s="9" t="inlineStr">
+        <is>
+          <t>Lipton Clear Green Tea</t>
+        </is>
+      </c>
+      <c r="C25" s="8" t="n">
+        <v>7</v>
+      </c>
+      <c r="D25" s="8" t="inlineStr">
+        <is>
+          <t>40 Bags</t>
+        </is>
+      </c>
+      <c r="E25" s="10" t="n">
+        <v>200</v>
+      </c>
+      <c r="F25" s="10" t="n">
+        <v>1400</v>
+      </c>
+    </row>
+    <row r="26">
+      <c r="A26" s="8" t="n">
+        <v>12</v>
+      </c>
+      <c r="B26" s="9" t="inlineStr">
+        <is>
+          <t>Bashundhara Facial Tissue Box</t>
+        </is>
+      </c>
+      <c r="C26" s="8" t="n">
+        <v>15</v>
+      </c>
+      <c r="D26" s="8" t="inlineStr">
+        <is>
+          <t>150x2 Ply</t>
+        </is>
+      </c>
+      <c r="E26" s="10" t="n">
+        <v>80</v>
+      </c>
+      <c r="F26" s="10" t="n">
+        <v>1200</v>
+      </c>
+    </row>
+    <row r="27">
+      <c r="A27" s="8" t="n">
+        <v>13</v>
+      </c>
+      <c r="B27" s="9" t="inlineStr">
+        <is>
+          <t>One Time Paper Cup (Beverage)</t>
+        </is>
+      </c>
+      <c r="C27" s="8" t="n">
+        <v>20000</v>
+      </c>
+      <c r="D27" s="8" t="inlineStr">
+        <is>
+          <t>250 ml</t>
+        </is>
+      </c>
+      <c r="E27" s="10" t="n">
+        <v>2</v>
+      </c>
+      <c r="F27" s="10" t="n">
+        <v>40000</v>
+      </c>
+    </row>
+    <row r="28">
+      <c r="A28" s="11" t="n"/>
+      <c r="B28" s="12" t="inlineStr">
+        <is>
+          <t>GRAND TOTAL (BDT)</t>
+        </is>
+      </c>
+      <c r="C28" s="11" t="n"/>
+      <c r="D28" s="11" t="n"/>
+      <c r="E28" s="11" t="n"/>
+      <c r="F28" s="13">
+        <f>SUM(F15:F27)</f>
         <v/>
       </c>
     </row>
-    <row r="15" ht="20" customHeight="1">
-      <c r="A15" s="12" t="n">
-        <v>2</v>
-      </c>
-      <c r="B15" s="13" t="inlineStr">
-        <is>
-          <t>Custom API Integration &amp; Microservices</t>
-        </is>
-      </c>
-      <c r="C15" s="12" t="n">
-        <v>25</v>
-      </c>
-      <c r="D15" s="14" t="n">
-        <v>120</v>
-      </c>
-      <c r="E15" s="14">
-        <f>C15*D15</f>
-        <v/>
-      </c>
-    </row>
-    <row r="16" ht="20" customHeight="1">
-      <c r="A16" s="9" t="n">
-        <v>3</v>
-      </c>
-      <c r="B16" s="10" t="inlineStr">
-        <is>
-          <t>Automated CI/CD Pipeline Implementation</t>
-        </is>
-      </c>
-      <c r="C16" s="9" t="n">
-        <v>15</v>
-      </c>
-      <c r="D16" s="11" t="n">
-        <v>110</v>
-      </c>
-      <c r="E16" s="11">
-        <f>C16*D16</f>
-        <v/>
-      </c>
-    </row>
-    <row r="17" ht="20" customHeight="1">
-      <c r="A17" s="12" t="n">
-        <v>4</v>
-      </c>
-      <c r="B17" s="13" t="inlineStr">
-        <is>
-          <t>High-Availability Database Clustering</t>
-        </is>
-      </c>
-      <c r="C17" s="12" t="n">
-        <v>20</v>
-      </c>
-      <c r="D17" s="14" t="n">
-        <v>140</v>
-      </c>
-      <c r="E17" s="14">
-        <f>C17*D17</f>
-        <v/>
-      </c>
-    </row>
-    <row r="18" ht="20" customHeight="1">
-      <c r="A18" s="9" t="n">
-        <v>5</v>
-      </c>
-      <c r="B18" s="10" t="inlineStr">
-        <is>
-          <t>Security Audit &amp; Vulnerability Assessment</t>
-        </is>
-      </c>
-      <c r="C18" s="9" t="n">
-        <v>1</v>
-      </c>
-      <c r="D18" s="11" t="n">
-        <v>1850</v>
-      </c>
-      <c r="E18" s="11">
-        <f>C18*D18</f>
-        <v/>
-      </c>
-    </row>
-    <row r="19" ht="20" customHeight="1">
-      <c r="A19" s="12" t="n">
-        <v>6</v>
-      </c>
-      <c r="B19" s="13" t="inlineStr">
-        <is>
-          <t>Dedicated Premium Support (Monthly SLA)</t>
-        </is>
-      </c>
-      <c r="C19" s="12" t="n">
-        <v>1</v>
-      </c>
-      <c r="D19" s="14" t="n">
-        <v>950</v>
-      </c>
-      <c r="E19" s="14">
-        <f>C19*D19</f>
-        <v/>
-      </c>
-    </row>
-    <row r="21">
-      <c r="D21" s="15" t="inlineStr">
-        <is>
-          <t>Subtotal:</t>
-        </is>
-      </c>
-      <c r="E21" s="16">
-        <f>SUM(E14:E19)</f>
-        <v/>
-      </c>
-    </row>
-    <row r="22">
-      <c r="D22" s="5" t="inlineStr">
-        <is>
-          <t>Tax / VAT (8.5%):</t>
-        </is>
-      </c>
-      <c r="E22" s="17">
-        <f>E21*0.085</f>
-        <v/>
-      </c>
-    </row>
-    <row r="23" ht="24" customHeight="1">
-      <c r="D23" s="18" t="inlineStr">
-        <is>
-          <t>Total Due (USD):</t>
-        </is>
-      </c>
-      <c r="E23" s="19">
-        <f>E21+E22</f>
-        <v/>
-      </c>
-    </row>
-    <row r="26">
-      <c r="A26" s="3" t="inlineStr">
-        <is>
-          <t>Bank Wire Transfer Details:</t>
-        </is>
-      </c>
-      <c r="D26" s="15" t="inlineStr">
-        <is>
-          <t>Authorized Signatory:</t>
-        </is>
-      </c>
-    </row>
-    <row r="27">
-      <c r="A27" s="4" t="inlineStr">
-        <is>
-          <t>Bank: Pacific National Commercial Bank</t>
-        </is>
-      </c>
-    </row>
-    <row r="28">
-      <c r="A28" s="4" t="inlineStr">
-        <is>
-          <t>Routing / ABA: 121000358</t>
-        </is>
-      </c>
-    </row>
-    <row r="29">
-      <c r="A29" s="4" t="inlineStr">
-        <is>
-          <t>Account No: 9874-4501-9238</t>
-        </is>
-      </c>
-    </row>
     <row r="30">
-      <c r="A30" s="4" t="inlineStr">
-        <is>
-          <t>SWIFT/BIC: PNCBUS33SF</t>
-        </is>
-      </c>
-      <c r="D30" s="5" t="inlineStr">
-        <is>
-          <t>--------------------------------------</t>
-        </is>
-      </c>
-    </row>
-    <row r="31">
-      <c r="D31" s="15" t="inlineStr">
-        <is>
-          <t>Alex Morgan, Managing Director</t>
+      <c r="B30" s="1" t="inlineStr">
+        <is>
+          <t>Amount in Words: One Lac Thirteen Thousand Seven Taka Only.</t>
+        </is>
+      </c>
+    </row>
+    <row r="34">
+      <c r="E34" s="1" t="inlineStr">
+        <is>
+          <t>MD. PARVES HOSSAN RAJIB</t>
+        </is>
+      </c>
+    </row>
+    <row r="35">
+      <c r="E35" s="3" t="inlineStr">
+        <is>
+          <t>PROPRIETOR</t>
+        </is>
+      </c>
+    </row>
+    <row r="36">
+      <c r="E36" s="1" t="inlineStr">
+        <is>
+          <t>SARWAR GENERAL STORE</t>
         </is>
       </c>
     </row>
   </sheetData>
-  <mergeCells count="5">
-    <mergeCell ref="D30:E30"/>
-    <mergeCell ref="A2:E2"/>
-    <mergeCell ref="D31:E31"/>
-    <mergeCell ref="D26:E26"/>
-    <mergeCell ref="A3:E3"/>
+  <mergeCells count="1">
+    <mergeCell ref="B12:F12"/>
   </mergeCells>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
-  <pageSetup orientation="portrait" paperSize="9" fitToHeight="0" fitToWidth="1"/>
+  <pageSetup orientation="portrait" paperSize="9"/>
 </worksheet>
 </file>
--- a/backend/samples/sample_invoice.xlsx
+++ b/backend/samples/sample_invoice.xlsx
@@ -7,7 +7,7 @@
     <workbookView visibility="visible" minimized="0" showHorizontalScroll="1" showVerticalScroll="1" showSheetTabs="1" tabRatio="600" firstSheet="0" activeTab="0" autoFilterDateGrouping="1"/>
   </bookViews>
   <sheets>
-    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Bill" sheetId="1" state="visible" r:id="rId1"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Tax Invoice" sheetId="1" state="visible" r:id="rId1"/>
   </sheets>
   <definedNames/>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
@@ -16,8 +16,10 @@
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
-  <numFmts count="0"/>
-  <fonts count="4">
+  <numFmts count="1">
+    <numFmt numFmtId="164" formatCode="$#,##0.00"/>
+  </numFmts>
+  <fonts count="7">
     <font>
       <name val="Calibri"/>
       <family val="2"/>
@@ -26,21 +28,41 @@
       <scheme val="minor"/>
     </font>
     <font>
-      <name val="Calibri"/>
+      <name val="Segoe UI"/>
       <b val="1"/>
-      <sz val="11"/>
+      <color rgb="001E3A8A"/>
+      <sz val="16"/>
     </font>
     <font>
-      <name val="Calibri"/>
+      <name val="Segoe UI"/>
+      <color rgb="004B5563"/>
       <sz val="10"/>
     </font>
     <font>
-      <name val="Calibri"/>
+      <name val="Segoe UI"/>
       <b val="1"/>
-      <sz val="15"/>
+      <color rgb="00111827"/>
+      <sz val="10"/>
+    </font>
+    <font>
+      <name val="Segoe UI"/>
+      <color rgb="001F2937"/>
+      <sz val="10"/>
+    </font>
+    <font>
+      <name val="Segoe UI"/>
+      <b val="1"/>
+      <color rgb="00FFFFFF"/>
+      <sz val="10"/>
+    </font>
+    <font>
+      <name val="Segoe UI"/>
+      <b val="1"/>
+      <color rgb="001E3A8A"/>
+      <sz val="11"/>
     </font>
   </fonts>
-  <fills count="3">
+  <fills count="5">
     <fill>
       <patternFill/>
     </fill>
@@ -49,12 +71,24 @@
     </fill>
     <fill>
       <patternFill patternType="solid">
-        <fgColor rgb="00F1F5F9"/>
-        <bgColor rgb="00F1F5F9"/>
+        <fgColor rgb="001E3A8A"/>
+        <bgColor rgb="001E3A8A"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="00F9FAFB"/>
+        <bgColor rgb="00F9FAFB"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="00EFF6FF"/>
+        <bgColor rgb="00EFF6FF"/>
       </patternFill>
     </fill>
   </fills>
-  <borders count="2">
+  <borders count="3">
     <border>
       <left/>
       <right/>
@@ -64,51 +98,81 @@
     </border>
     <border>
       <left style="thin">
-        <color rgb="00CBD5E1"/>
+        <color rgb="00D1D5DB"/>
       </left>
       <right style="thin">
-        <color rgb="00CBD5E1"/>
+        <color rgb="00D1D5DB"/>
       </right>
       <top style="thin">
-        <color rgb="00CBD5E1"/>
+        <color rgb="00D1D5DB"/>
       </top>
       <bottom style="thin">
-        <color rgb="00CBD5E1"/>
+        <color rgb="00D1D5DB"/>
+      </bottom>
+    </border>
+    <border>
+      <top style="thin">
+        <color rgb="00D1D5DB"/>
+      </top>
+      <bottom style="double">
+        <color rgb="001E3A8A"/>
       </bottom>
     </border>
   </borders>
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="14">
+  <cellXfs count="20">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
-    <xf numFmtId="0" fontId="1" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="0" fontId="4" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="0" fontId="4" fillId="0" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="right"/>
     </xf>
-    <xf numFmtId="0" fontId="2" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="0" fontId="5" fillId="2" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="2" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="left" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="2" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="right" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="4" fillId="0" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="4" fillId="0" borderId="1" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="164" fontId="4" fillId="0" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="right"/>
+    </xf>
+    <xf numFmtId="0" fontId="4" fillId="3" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="4" fillId="3" borderId="1" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="164" fontId="4" fillId="3" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="right"/>
+    </xf>
     <xf numFmtId="0" fontId="3" fillId="0" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="1" fillId="2" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="1" fillId="2" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
-      <alignment horizontal="left"/>
-    </xf>
-    <xf numFmtId="0" fontId="1" fillId="2" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="right"/>
     </xf>
-    <xf numFmtId="0" fontId="2" fillId="0" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="0" borderId="1" pivotButton="0" quotePrefix="0" xfId="0"/>
-    <xf numFmtId="4" fontId="2" fillId="0" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+    <xf numFmtId="164" fontId="3" fillId="0" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="right"/>
     </xf>
-    <xf numFmtId="0" fontId="0" fillId="2" borderId="1" pivotButton="0" quotePrefix="0" xfId="0"/>
-    <xf numFmtId="0" fontId="1" fillId="2" borderId="1" pivotButton="0" quotePrefix="0" xfId="0"/>
-    <xf numFmtId="4" fontId="1" fillId="2" borderId="1" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="164" fontId="4" fillId="0" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="right"/>
+    </xf>
+    <xf numFmtId="0" fontId="6" fillId="4" borderId="2" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="right" vertical="center"/>
+    </xf>
+    <xf numFmtId="164" fontId="6" fillId="4" borderId="2" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="right" vertical="center"/>
+    </xf>
   </cellXfs>
   <cellStyles count="1">
     <cellStyle name="Normal" xfId="0" builtinId="0" hidden="0"/>
@@ -472,461 +536,350 @@
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <sheetPr>
     <outlinePr summaryBelow="1" summaryRight="1"/>
-    <pageSetUpPr/>
+    <pageSetUpPr fitToPage="1"/>
   </sheetPr>
-  <dimension ref="A4:F36"/>
+  <dimension ref="A2:E31"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="6" customWidth="1" min="1" max="1"/>
-    <col width="34" customWidth="1" min="2" max="2"/>
-    <col width="11" customWidth="1" min="3" max="3"/>
-    <col width="12" customWidth="1" min="4" max="4"/>
+    <col width="30" customWidth="1" min="2" max="2"/>
+    <col width="12" customWidth="1" min="3" max="3"/>
+    <col width="14" customWidth="1" min="4" max="4"/>
     <col width="16" customWidth="1" min="5" max="5"/>
-    <col width="18" customWidth="1" min="6" max="6"/>
   </cols>
   <sheetData>
-    <row r="1" ht="20" customHeight="1"/>
-    <row r="2" ht="20" customHeight="1"/>
-    <row r="3" ht="15" customHeight="1"/>
-    <row r="4">
-      <c r="B4" s="1" t="inlineStr">
-        <is>
-          <t>Ref: W.B/Bill # 0072/26</t>
-        </is>
-      </c>
-      <c r="F4" s="2" t="inlineStr">
-        <is>
-          <t>Date: 14.06.2026</t>
+    <row r="2" ht="28" customHeight="1">
+      <c r="A2" s="1" t="inlineStr">
+        <is>
+          <t>COMMERCIAL INVOICE</t>
+        </is>
+      </c>
+    </row>
+    <row r="3">
+      <c r="A3" s="2" t="inlineStr">
+        <is>
+          <t>Original For Recipient | GST/VAT Compliant</t>
+        </is>
+      </c>
+    </row>
+    <row r="5">
+      <c r="A5" s="3" t="inlineStr">
+        <is>
+          <t>Invoice No:</t>
+        </is>
+      </c>
+      <c r="B5" s="4" t="inlineStr">
+        <is>
+          <t>INV-2026-0842</t>
+        </is>
+      </c>
+      <c r="D5" s="3" t="inlineStr">
+        <is>
+          <t>Invoice Date:</t>
+        </is>
+      </c>
+      <c r="E5" s="5" t="inlineStr">
+        <is>
+          <t>18-Oct-2026</t>
         </is>
       </c>
     </row>
     <row r="6">
-      <c r="B6" s="1" t="inlineStr">
-        <is>
-          <t>To</t>
-        </is>
-      </c>
-    </row>
-    <row r="7">
-      <c r="B7" s="1" t="inlineStr">
-        <is>
-          <t>The World Bank Office</t>
+      <c r="A6" s="3" t="inlineStr">
+        <is>
+          <t>Due Date:</t>
+        </is>
+      </c>
+      <c r="B6" s="4" t="inlineStr">
+        <is>
+          <t>02-Nov-2026</t>
+        </is>
+      </c>
+      <c r="D6" s="3" t="inlineStr">
+        <is>
+          <t>Payment Terms:</t>
+        </is>
+      </c>
+      <c r="E6" s="5" t="inlineStr">
+        <is>
+          <t>Net 15 Days</t>
         </is>
       </c>
     </row>
     <row r="8">
+      <c r="A8" s="3" t="inlineStr">
+        <is>
+          <t>Billed To:</t>
+        </is>
+      </c>
       <c r="B8" s="3" t="inlineStr">
         <is>
-          <t>Plot # E-32, Agargoan</t>
+          <t>Horizon Global Enterprises Ltd.</t>
         </is>
       </c>
     </row>
     <row r="9">
-      <c r="B9" s="3" t="inlineStr">
-        <is>
-          <t>Sher-e-Bangla Nagar, Dhaka.</t>
-        </is>
-      </c>
-    </row>
-    <row r="12">
-      <c r="B12" s="4" t="inlineStr">
-        <is>
-          <t>Bill for Supply Items</t>
-        </is>
-      </c>
-    </row>
-    <row r="14">
-      <c r="A14" s="5" t="inlineStr">
-        <is>
-          <t>SI#</t>
-        </is>
-      </c>
-      <c r="B14" s="6" t="inlineStr">
-        <is>
-          <t>Item Name &amp; Description</t>
-        </is>
-      </c>
-      <c r="C14" s="5" t="inlineStr">
-        <is>
-          <t>Quantity</t>
-        </is>
-      </c>
-      <c r="D14" s="5" t="inlineStr">
-        <is>
-          <t>Pack Size</t>
-        </is>
-      </c>
-      <c r="E14" s="7" t="inlineStr">
-        <is>
-          <t>Unit Price (BDT)</t>
-        </is>
-      </c>
-      <c r="F14" s="7" t="inlineStr">
-        <is>
-          <t>Total Amount (BDT)</t>
-        </is>
-      </c>
-    </row>
-    <row r="15">
-      <c r="A15" s="8" t="n">
+      <c r="B9" s="4" t="inlineStr">
+        <is>
+          <t>450 Innovation Parkway, Suite 800</t>
+        </is>
+      </c>
+    </row>
+    <row r="10">
+      <c r="B10" s="4" t="inlineStr">
+        <is>
+          <t>San Francisco, CA 94107</t>
+        </is>
+      </c>
+    </row>
+    <row r="11">
+      <c r="B11" s="4" t="inlineStr">
+        <is>
+          <t>Attn: Accounts Payable (finance@horizonglobal.com)</t>
+        </is>
+      </c>
+    </row>
+    <row r="13" ht="24" customHeight="1">
+      <c r="A13" s="6" t="inlineStr">
+        <is>
+          <t>#</t>
+        </is>
+      </c>
+      <c r="B13" s="7" t="inlineStr">
+        <is>
+          <t>Item Description</t>
+        </is>
+      </c>
+      <c r="C13" s="6" t="inlineStr">
+        <is>
+          <t>Qty</t>
+        </is>
+      </c>
+      <c r="D13" s="8" t="inlineStr">
+        <is>
+          <t>Unit Price</t>
+        </is>
+      </c>
+      <c r="E13" s="8" t="inlineStr">
+        <is>
+          <t>Total (USD)</t>
+        </is>
+      </c>
+    </row>
+    <row r="14" ht="20" customHeight="1">
+      <c r="A14" s="9" t="n">
         <v>1</v>
       </c>
-      <c r="B15" s="9" t="inlineStr">
-        <is>
-          <t>Ispahani Tea Bags</t>
-        </is>
-      </c>
-      <c r="C15" s="8" t="n">
-        <v>127</v>
-      </c>
-      <c r="D15" s="8" t="inlineStr">
-        <is>
-          <t>50 Bags</t>
-        </is>
-      </c>
-      <c r="E15" s="10" t="n">
-        <v>94</v>
-      </c>
-      <c r="F15" s="10" t="n">
-        <v>11938</v>
-      </c>
-    </row>
-    <row r="16">
-      <c r="A16" s="8" t="n">
+      <c r="B14" s="10" t="inlineStr">
+        <is>
+          <t>Enterprise Cloud Architecture Consulting</t>
+        </is>
+      </c>
+      <c r="C14" s="9" t="n">
+        <v>40</v>
+      </c>
+      <c r="D14" s="11" t="n">
+        <v>150</v>
+      </c>
+      <c r="E14" s="11">
+        <f>C14*D14</f>
+        <v/>
+      </c>
+    </row>
+    <row r="15" ht="20" customHeight="1">
+      <c r="A15" s="12" t="n">
         <v>2</v>
       </c>
-      <c r="B16" s="9" t="inlineStr">
-        <is>
-          <t>Nescafe Classic Coffee</t>
-        </is>
-      </c>
-      <c r="C16" s="8" t="n">
-        <v>24</v>
-      </c>
-      <c r="D16" s="8" t="inlineStr">
-        <is>
-          <t>200 gm</t>
-        </is>
-      </c>
-      <c r="E16" s="10" t="n">
+      <c r="B15" s="13" t="inlineStr">
+        <is>
+          <t>Custom API Integration &amp; Microservices</t>
+        </is>
+      </c>
+      <c r="C15" s="12" t="n">
+        <v>25</v>
+      </c>
+      <c r="D15" s="14" t="n">
+        <v>120</v>
+      </c>
+      <c r="E15" s="14">
+        <f>C15*D15</f>
+        <v/>
+      </c>
+    </row>
+    <row r="16" ht="20" customHeight="1">
+      <c r="A16" s="9" t="n">
+        <v>3</v>
+      </c>
+      <c r="B16" s="10" t="inlineStr">
+        <is>
+          <t>Automated CI/CD Pipeline Implementation</t>
+        </is>
+      </c>
+      <c r="C16" s="9" t="n">
+        <v>15</v>
+      </c>
+      <c r="D16" s="11" t="n">
+        <v>110</v>
+      </c>
+      <c r="E16" s="11">
+        <f>C16*D16</f>
+        <v/>
+      </c>
+    </row>
+    <row r="17" ht="20" customHeight="1">
+      <c r="A17" s="12" t="n">
+        <v>4</v>
+      </c>
+      <c r="B17" s="13" t="inlineStr">
+        <is>
+          <t>High-Availability Database Clustering</t>
+        </is>
+      </c>
+      <c r="C17" s="12" t="n">
+        <v>20</v>
+      </c>
+      <c r="D17" s="14" t="n">
+        <v>140</v>
+      </c>
+      <c r="E17" s="14">
+        <f>C17*D17</f>
+        <v/>
+      </c>
+    </row>
+    <row r="18" ht="20" customHeight="1">
+      <c r="A18" s="9" t="n">
+        <v>5</v>
+      </c>
+      <c r="B18" s="10" t="inlineStr">
+        <is>
+          <t>Security Audit &amp; Vulnerability Assessment</t>
+        </is>
+      </c>
+      <c r="C18" s="9" t="n">
+        <v>1</v>
+      </c>
+      <c r="D18" s="11" t="n">
+        <v>1850</v>
+      </c>
+      <c r="E18" s="11">
+        <f>C18*D18</f>
+        <v/>
+      </c>
+    </row>
+    <row r="19" ht="20" customHeight="1">
+      <c r="A19" s="12" t="n">
+        <v>6</v>
+      </c>
+      <c r="B19" s="13" t="inlineStr">
+        <is>
+          <t>Dedicated Premium Support (Monthly SLA)</t>
+        </is>
+      </c>
+      <c r="C19" s="12" t="n">
+        <v>1</v>
+      </c>
+      <c r="D19" s="14" t="n">
         <v>950</v>
       </c>
-      <c r="F16" s="10" t="n">
-        <v>22800</v>
-      </c>
-    </row>
-    <row r="17">
-      <c r="A17" s="8" t="n">
-        <v>3</v>
-      </c>
-      <c r="B17" s="9" t="inlineStr">
-        <is>
-          <t>Diploma Full Cream Powder Milk</t>
-        </is>
-      </c>
-      <c r="C17" s="8" t="n">
-        <v>24</v>
-      </c>
-      <c r="D17" s="8" t="inlineStr">
-        <is>
-          <t>1 kg</t>
-        </is>
-      </c>
-      <c r="E17" s="10" t="n">
-        <v>935</v>
-      </c>
-      <c r="F17" s="10" t="n">
-        <v>22440</v>
-      </c>
-    </row>
-    <row r="18">
-      <c r="A18" s="8" t="n">
-        <v>4</v>
-      </c>
-      <c r="B18" s="9" t="inlineStr">
-        <is>
-          <t>Fresh White Sugar</t>
-        </is>
-      </c>
-      <c r="C18" s="8" t="n">
-        <v>51</v>
-      </c>
-      <c r="D18" s="8" t="inlineStr">
-        <is>
-          <t>1 kg</t>
-        </is>
-      </c>
-      <c r="E18" s="10" t="n">
-        <v>104</v>
-      </c>
-      <c r="F18" s="10" t="n">
-        <v>5304</v>
-      </c>
-    </row>
-    <row r="19">
-      <c r="A19" s="8" t="n">
-        <v>5</v>
-      </c>
-      <c r="B19" s="9" t="inlineStr">
-        <is>
-          <t>Canderel Sweetener (Square)</t>
-        </is>
-      </c>
-      <c r="C19" s="8" t="n">
-        <v>8</v>
-      </c>
-      <c r="D19" s="8" t="inlineStr">
-        <is>
-          <t>100 Tab</t>
-        </is>
-      </c>
-      <c r="E19" s="10" t="n">
-        <v>115</v>
-      </c>
-      <c r="F19" s="10" t="n">
-        <v>920</v>
-      </c>
-    </row>
-    <row r="20">
-      <c r="A20" s="8" t="n">
-        <v>6</v>
-      </c>
-      <c r="B20" s="9" t="inlineStr">
-        <is>
-          <t>Liquid Vim Dishwashing</t>
-        </is>
-      </c>
-      <c r="C20" s="8" t="n">
-        <v>15</v>
-      </c>
-      <c r="D20" s="8" t="inlineStr">
-        <is>
-          <t>500 ml</t>
-        </is>
-      </c>
-      <c r="E20" s="10" t="n">
-        <v>125</v>
-      </c>
-      <c r="F20" s="10" t="n">
-        <v>1875</v>
+      <c r="E19" s="14">
+        <f>C19*D19</f>
+        <v/>
       </c>
     </row>
     <row r="21">
-      <c r="A21" s="8" t="n">
-        <v>7</v>
-      </c>
-      <c r="B21" s="9" t="inlineStr">
-        <is>
-          <t>Jet Washing Powder</t>
-        </is>
-      </c>
-      <c r="C21" s="8" t="n">
-        <v>3</v>
-      </c>
-      <c r="D21" s="8" t="inlineStr">
-        <is>
-          <t>1 kg</t>
-        </is>
-      </c>
-      <c r="E21" s="10" t="n">
-        <v>280</v>
-      </c>
-      <c r="F21" s="10" t="n">
-        <v>840</v>
+      <c r="D21" s="15" t="inlineStr">
+        <is>
+          <t>Subtotal:</t>
+        </is>
+      </c>
+      <c r="E21" s="16">
+        <f>SUM(E14:E19)</f>
+        <v/>
       </c>
     </row>
     <row r="22">
-      <c r="A22" s="8" t="n">
-        <v>8</v>
-      </c>
-      <c r="B22" s="9" t="inlineStr">
-        <is>
-          <t>Lux Beauty Soap</t>
-        </is>
-      </c>
-      <c r="C22" s="8" t="n">
-        <v>6</v>
-      </c>
-      <c r="D22" s="8" t="inlineStr">
-        <is>
-          <t>100 gm</t>
-        </is>
-      </c>
-      <c r="E22" s="10" t="n">
-        <v>55</v>
-      </c>
-      <c r="F22" s="10" t="n">
-        <v>330</v>
-      </c>
-    </row>
-    <row r="23">
-      <c r="A23" s="8" t="n">
-        <v>9</v>
-      </c>
-      <c r="B23" s="9" t="inlineStr">
-        <is>
-          <t>Air Freshener (Godrej)</t>
-        </is>
-      </c>
-      <c r="C23" s="8" t="n">
-        <v>7</v>
-      </c>
-      <c r="D23" s="8" t="inlineStr">
-        <is>
-          <t>300 ml</t>
-        </is>
-      </c>
-      <c r="E23" s="10" t="n">
-        <v>280</v>
-      </c>
-      <c r="F23" s="10" t="n">
-        <v>1960</v>
-      </c>
-    </row>
-    <row r="24">
-      <c r="A24" s="8" t="n">
-        <v>10</v>
-      </c>
-      <c r="B24" s="9" t="inlineStr">
-        <is>
-          <t>ACI Aerosol Spray</t>
-        </is>
-      </c>
-      <c r="C24" s="8" t="n">
-        <v>5</v>
-      </c>
-      <c r="D24" s="8" t="inlineStr">
-        <is>
-          <t>475 ml</t>
-        </is>
-      </c>
-      <c r="E24" s="10" t="n">
-        <v>400</v>
-      </c>
-      <c r="F24" s="10" t="n">
-        <v>2000</v>
-      </c>
-    </row>
-    <row r="25">
-      <c r="A25" s="8" t="n">
-        <v>11</v>
-      </c>
-      <c r="B25" s="9" t="inlineStr">
-        <is>
-          <t>Lipton Clear Green Tea</t>
-        </is>
-      </c>
-      <c r="C25" s="8" t="n">
-        <v>7</v>
-      </c>
-      <c r="D25" s="8" t="inlineStr">
-        <is>
-          <t>40 Bags</t>
-        </is>
-      </c>
-      <c r="E25" s="10" t="n">
-        <v>200</v>
-      </c>
-      <c r="F25" s="10" t="n">
-        <v>1400</v>
+      <c r="D22" s="5" t="inlineStr">
+        <is>
+          <t>Tax / VAT (8.5%):</t>
+        </is>
+      </c>
+      <c r="E22" s="17">
+        <f>E21*0.085</f>
+        <v/>
+      </c>
+    </row>
+    <row r="23" ht="24" customHeight="1">
+      <c r="D23" s="18" t="inlineStr">
+        <is>
+          <t>Total Due (USD):</t>
+        </is>
+      </c>
+      <c r="E23" s="19">
+        <f>E21+E22</f>
+        <v/>
       </c>
     </row>
     <row r="26">
-      <c r="A26" s="8" t="n">
-        <v>12</v>
-      </c>
-      <c r="B26" s="9" t="inlineStr">
-        <is>
-          <t>Bashundhara Facial Tissue Box</t>
-        </is>
-      </c>
-      <c r="C26" s="8" t="n">
-        <v>15</v>
-      </c>
-      <c r="D26" s="8" t="inlineStr">
-        <is>
-          <t>150x2 Ply</t>
-        </is>
-      </c>
-      <c r="E26" s="10" t="n">
-        <v>80</v>
-      </c>
-      <c r="F26" s="10" t="n">
-        <v>1200</v>
+      <c r="A26" s="3" t="inlineStr">
+        <is>
+          <t>Bank Wire Transfer Details:</t>
+        </is>
+      </c>
+      <c r="D26" s="15" t="inlineStr">
+        <is>
+          <t>Authorized Signatory:</t>
+        </is>
       </c>
     </row>
     <row r="27">
-      <c r="A27" s="8" t="n">
-        <v>13</v>
-      </c>
-      <c r="B27" s="9" t="inlineStr">
-        <is>
-          <t>One Time Paper Cup (Beverage)</t>
-        </is>
-      </c>
-      <c r="C27" s="8" t="n">
-        <v>20000</v>
-      </c>
-      <c r="D27" s="8" t="inlineStr">
-        <is>
-          <t>250 ml</t>
-        </is>
-      </c>
-      <c r="E27" s="10" t="n">
-        <v>2</v>
-      </c>
-      <c r="F27" s="10" t="n">
-        <v>40000</v>
+      <c r="A27" s="4" t="inlineStr">
+        <is>
+          <t>Bank: Pacific National Commercial Bank</t>
+        </is>
       </c>
     </row>
     <row r="28">
-      <c r="A28" s="11" t="n"/>
-      <c r="B28" s="12" t="inlineStr">
-        <is>
-          <t>GRAND TOTAL (BDT)</t>
-        </is>
-      </c>
-      <c r="C28" s="11" t="n"/>
-      <c r="D28" s="11" t="n"/>
-      <c r="E28" s="11" t="n"/>
-      <c r="F28" s="13">
-        <f>SUM(F15:F27)</f>
-        <v/>
+      <c r="A28" s="4" t="inlineStr">
+        <is>
+          <t>Routing / ABA: 121000358</t>
+        </is>
+      </c>
+    </row>
+    <row r="29">
+      <c r="A29" s="4" t="inlineStr">
+        <is>
+          <t>Account No: 9874-4501-9238</t>
+        </is>
       </c>
     </row>
     <row r="30">
-      <c r="B30" s="1" t="inlineStr">
-        <is>
-          <t>Amount in Words: One Lac Thirteen Thousand Seven Taka Only.</t>
-        </is>
-      </c>
-    </row>
-    <row r="34">
-      <c r="E34" s="1" t="inlineStr">
-        <is>
-          <t>MD. PARVES HOSSAN RAJIB</t>
-        </is>
-      </c>
-    </row>
-    <row r="35">
-      <c r="E35" s="3" t="inlineStr">
-        <is>
-          <t>PROPRIETOR</t>
-        </is>
-      </c>
-    </row>
-    <row r="36">
-      <c r="E36" s="1" t="inlineStr">
-        <is>
-          <t>SARWAR GENERAL STORE</t>
+      <c r="A30" s="4" t="inlineStr">
+        <is>
+          <t>SWIFT/BIC: PNCBUS33SF</t>
+        </is>
+      </c>
+      <c r="D30" s="5" t="inlineStr">
+        <is>
+          <t>--------------------------------------</t>
+        </is>
+      </c>
+    </row>
+    <row r="31">
+      <c r="D31" s="15" t="inlineStr">
+        <is>
+          <t>Alex Morgan, Managing Director</t>
         </is>
       </c>
     </row>
   </sheetData>
-  <mergeCells count="1">
-    <mergeCell ref="B12:F12"/>
+  <mergeCells count="5">
+    <mergeCell ref="D30:E30"/>
+    <mergeCell ref="A2:E2"/>
+    <mergeCell ref="D31:E31"/>
+    <mergeCell ref="D26:E26"/>
+    <mergeCell ref="A3:E3"/>
   </mergeCells>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
-  <pageSetup orientation="portrait" paperSize="9"/>
+  <pageSetup orientation="portrait" paperSize="9" fitToHeight="0" fitToWidth="1"/>
 </worksheet>
 </file>